--- a/resources/tools/ehr-adoption-check.xlsx
+++ b/resources/tools/ehr-adoption-check.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{3775AF47-F34C-4360-8177-866CD8AAC42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD6AE703-F982-4794-9EA3-87B15CF69055}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{64DD9714-B0DC-489B-ABE8-354EE257C309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0" xr2:uid="{64DD9714-B0DC-489B-ABE8-354EE257C309}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="2" r:id="rId1"/>
